--- a/24 math game.xlsx
+++ b/24 math game.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA10FC02-ABFF-4B10-9E3A-DDAF75492A18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17940" yWindow="650" windowWidth="16460" windowHeight="13030" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17940" yWindow="648" windowWidth="16464" windowHeight="13032" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Single Digits" sheetId="1" r:id="rId1"/>
     <sheet name="Integers" sheetId="2" r:id="rId2"/>
+    <sheet name="Fractions&amp;Decimals" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1554" uniqueCount="72">
   <si>
     <t>Style</t>
   </si>
@@ -51,11 +51,203 @@
   <si>
     <t>Integers</t>
   </si>
+  <si>
+    <t>Fractions/Decimals</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>.2</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>.5</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>2.2</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>.8</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>.3</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>.1</t>
+  </si>
+  <si>
+    <t>1.5</t>
+  </si>
+  <si>
+    <t>1/2</t>
+  </si>
+  <si>
+    <t>3/8</t>
+  </si>
+  <si>
+    <t>1/3</t>
+  </si>
+  <si>
+    <t>1/6</t>
+  </si>
+  <si>
+    <t>1/4</t>
+  </si>
+  <si>
+    <t>2/3</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
+    <t>.4</t>
+  </si>
+  <si>
+    <t>.6</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>2.5</t>
+  </si>
+  <si>
+    <t>5/8</t>
+  </si>
+  <si>
+    <t>4.6</t>
+  </si>
+  <si>
+    <t>8.6</t>
+  </si>
+  <si>
+    <t>1/8</t>
+  </si>
+  <si>
+    <t>.7</t>
+  </si>
+  <si>
+    <t>2.8</t>
+  </si>
+  <si>
+    <t>2.4</t>
+  </si>
+  <si>
+    <t>6.7</t>
+  </si>
+  <si>
+    <t>5.7</t>
+  </si>
+  <si>
+    <t>6.4</t>
+  </si>
+  <si>
+    <t>3.2</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>3.6</t>
+  </si>
+  <si>
+    <t>7/8</t>
+  </si>
+  <si>
+    <t>3/4</t>
+  </si>
+  <si>
+    <t>5/6</t>
+  </si>
+  <si>
+    <t>3/2</t>
+  </si>
+  <si>
+    <t>5.6</t>
+  </si>
+  <si>
+    <t>5.4</t>
+  </si>
+  <si>
+    <t>4.2</t>
+  </si>
+  <si>
+    <t>1.8</t>
+  </si>
+  <si>
+    <t>2.1</t>
+  </si>
+  <si>
+    <t>7.5</t>
+  </si>
+  <si>
+    <t>1.2</t>
+  </si>
+  <si>
+    <t>3.8</t>
+  </si>
+  <si>
+    <t>1.4</t>
+  </si>
+  <si>
+    <t>8.5</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>7.2</t>
+  </si>
+  <si>
+    <t>6.5</t>
+  </si>
+  <si>
+    <t>3.3</t>
+  </si>
+  <si>
+    <t>4.5</t>
+  </si>
+  <si>
+    <t>5.5</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>2.7</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -85,10 +277,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -369,20 +567,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F193"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.90625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.08984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.90625" style="1"/>
+    <col min="1" max="1" width="10.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -402,7 +600,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -422,7 +620,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -442,7 +640,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -462,7 +660,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -482,7 +680,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
@@ -502,7 +700,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -522,7 +720,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -542,7 +740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
@@ -562,7 +760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>6</v>
       </c>
@@ -582,7 +780,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>6</v>
       </c>
@@ -602,7 +800,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>6</v>
       </c>
@@ -622,7 +820,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>6</v>
       </c>
@@ -642,7 +840,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>6</v>
       </c>
@@ -662,7 +860,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>6</v>
       </c>
@@ -682,7 +880,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>6</v>
       </c>
@@ -702,7 +900,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>6</v>
       </c>
@@ -722,7 +920,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>6</v>
       </c>
@@ -742,7 +940,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>6</v>
       </c>
@@ -762,7 +960,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>6</v>
       </c>
@@ -782,7 +980,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>6</v>
       </c>
@@ -802,7 +1000,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>6</v>
       </c>
@@ -822,7 +1020,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>6</v>
       </c>
@@ -842,7 +1040,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>6</v>
       </c>
@@ -862,7 +1060,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>6</v>
       </c>
@@ -882,7 +1080,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>6</v>
       </c>
@@ -902,7 +1100,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>6</v>
       </c>
@@ -922,7 +1120,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>6</v>
       </c>
@@ -942,7 +1140,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>6</v>
       </c>
@@ -962,7 +1160,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>6</v>
       </c>
@@ -982,7 +1180,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>6</v>
       </c>
@@ -1002,7 +1200,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>6</v>
       </c>
@@ -1022,7 +1220,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>6</v>
       </c>
@@ -1042,7 +1240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>6</v>
       </c>
@@ -1062,7 +1260,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>6</v>
       </c>
@@ -1082,7 +1280,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>6</v>
       </c>
@@ -1102,7 +1300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>6</v>
       </c>
@@ -1122,7 +1320,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>6</v>
       </c>
@@ -1142,7 +1340,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>6</v>
       </c>
@@ -1162,7 +1360,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>6</v>
       </c>
@@ -1182,7 +1380,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>6</v>
       </c>
@@ -1202,7 +1400,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>6</v>
       </c>
@@ -1222,7 +1420,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>6</v>
       </c>
@@ -1242,7 +1440,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>6</v>
       </c>
@@ -1262,7 +1460,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>6</v>
       </c>
@@ -1282,7 +1480,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>6</v>
       </c>
@@ -1302,7 +1500,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>6</v>
       </c>
@@ -1322,7 +1520,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>6</v>
       </c>
@@ -1342,7 +1540,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>6</v>
       </c>
@@ -1362,7 +1560,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>6</v>
       </c>
@@ -1382,7 +1580,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>6</v>
       </c>
@@ -1402,7 +1600,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>6</v>
       </c>
@@ -1422,7 +1620,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>6</v>
       </c>
@@ -1442,7 +1640,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>6</v>
       </c>
@@ -1462,7 +1660,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>6</v>
       </c>
@@ -1482,7 +1680,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>6</v>
       </c>
@@ -1502,7 +1700,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>6</v>
       </c>
@@ -1522,7 +1720,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>6</v>
       </c>
@@ -1542,7 +1740,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>6</v>
       </c>
@@ -1562,7 +1760,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>6</v>
       </c>
@@ -1582,7 +1780,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>6</v>
       </c>
@@ -1602,7 +1800,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>6</v>
       </c>
@@ -1622,7 +1820,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>6</v>
       </c>
@@ -1642,7 +1840,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>6</v>
       </c>
@@ -1662,7 +1860,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>6</v>
       </c>
@@ -1682,7 +1880,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>6</v>
       </c>
@@ -1702,7 +1900,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>6</v>
       </c>
@@ -1722,7 +1920,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>6</v>
       </c>
@@ -1742,7 +1940,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>6</v>
       </c>
@@ -1762,7 +1960,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>6</v>
       </c>
@@ -1782,7 +1980,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>6</v>
       </c>
@@ -1802,7 +2000,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>6</v>
       </c>
@@ -1822,7 +2020,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>6</v>
       </c>
@@ -1842,7 +2040,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>6</v>
       </c>
@@ -1862,7 +2060,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>6</v>
       </c>
@@ -1882,7 +2080,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>6</v>
       </c>
@@ -1902,7 +2100,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>6</v>
       </c>
@@ -1922,7 +2120,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>6</v>
       </c>
@@ -1942,7 +2140,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>6</v>
       </c>
@@ -1962,7 +2160,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>6</v>
       </c>
@@ -1982,7 +2180,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>6</v>
       </c>
@@ -2002,7 +2200,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>6</v>
       </c>
@@ -2022,7 +2220,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
         <v>6</v>
       </c>
@@ -2042,7 +2240,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>6</v>
       </c>
@@ -2062,7 +2260,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>6</v>
       </c>
@@ -2082,7 +2280,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>6</v>
       </c>
@@ -2102,7 +2300,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
         <v>6</v>
       </c>
@@ -2122,7 +2320,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
         <v>6</v>
       </c>
@@ -2142,7 +2340,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>6</v>
       </c>
@@ -2162,7 +2360,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>6</v>
       </c>
@@ -2182,7 +2380,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
         <v>6</v>
       </c>
@@ -2202,7 +2400,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>6</v>
       </c>
@@ -2222,7 +2420,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
         <v>6</v>
       </c>
@@ -2242,7 +2440,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
         <v>6</v>
       </c>
@@ -2262,7 +2460,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
         <v>6</v>
       </c>
@@ -2282,7 +2480,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
         <v>6</v>
       </c>
@@ -2302,7 +2500,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
         <v>6</v>
       </c>
@@ -2322,7 +2520,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
         <v>6</v>
       </c>
@@ -2342,7 +2540,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
         <v>6</v>
       </c>
@@ -2362,7 +2560,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
         <v>6</v>
       </c>
@@ -2382,7 +2580,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
         <v>6</v>
       </c>
@@ -2402,7 +2600,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
         <v>6</v>
       </c>
@@ -2422,7 +2620,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
         <v>6</v>
       </c>
@@ -2442,7 +2640,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
         <v>6</v>
       </c>
@@ -2462,7 +2660,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
         <v>6</v>
       </c>
@@ -2482,7 +2680,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
         <v>6</v>
       </c>
@@ -2502,7 +2700,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
         <v>6</v>
       </c>
@@ -2522,7 +2720,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
         <v>6</v>
       </c>
@@ -2542,7 +2740,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
         <v>6</v>
       </c>
@@ -2562,7 +2760,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
         <v>6</v>
       </c>
@@ -2582,7 +2780,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
         <v>6</v>
       </c>
@@ -2602,7 +2800,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
         <v>6</v>
       </c>
@@ -2622,7 +2820,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
         <v>6</v>
       </c>
@@ -2642,7 +2840,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
         <v>6</v>
       </c>
@@ -2662,7 +2860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
         <v>6</v>
       </c>
@@ -2682,7 +2880,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
         <v>6</v>
       </c>
@@ -2702,7 +2900,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
         <v>6</v>
       </c>
@@ -2722,7 +2920,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
         <v>6</v>
       </c>
@@ -2742,7 +2940,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
         <v>6</v>
       </c>
@@ -2762,7 +2960,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
         <v>6</v>
       </c>
@@ -2782,7 +2980,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
         <v>6</v>
       </c>
@@ -2802,7 +3000,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
         <v>6</v>
       </c>
@@ -2822,7 +3020,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
         <v>6</v>
       </c>
@@ -2842,7 +3040,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
         <v>6</v>
       </c>
@@ -2862,7 +3060,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
         <v>6</v>
       </c>
@@ -2882,7 +3080,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
         <v>6</v>
       </c>
@@ -2902,7 +3100,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
         <v>6</v>
       </c>
@@ -2922,7 +3120,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
         <v>6</v>
       </c>
@@ -2942,7 +3140,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
         <v>6</v>
       </c>
@@ -2962,7 +3160,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
         <v>6</v>
       </c>
@@ -2982,7 +3180,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
         <v>6</v>
       </c>
@@ -3002,7 +3200,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
         <v>6</v>
       </c>
@@ -3022,7 +3220,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
         <v>6</v>
       </c>
@@ -3042,7 +3240,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
         <v>6</v>
       </c>
@@ -3062,7 +3260,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
         <v>6</v>
       </c>
@@ -3082,7 +3280,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
         <v>6</v>
       </c>
@@ -3102,7 +3300,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
         <v>6</v>
       </c>
@@ -3122,7 +3320,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
         <v>6</v>
       </c>
@@ -3142,7 +3340,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
         <v>6</v>
       </c>
@@ -3162,7 +3360,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
         <v>6</v>
       </c>
@@ -3182,7 +3380,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
         <v>6</v>
       </c>
@@ -3202,7 +3400,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
         <v>6</v>
       </c>
@@ -3222,7 +3420,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
         <v>6</v>
       </c>
@@ -3242,7 +3440,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
         <v>6</v>
       </c>
@@ -3262,7 +3460,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
         <v>6</v>
       </c>
@@ -3282,7 +3480,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
         <v>6</v>
       </c>
@@ -3302,7 +3500,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
         <v>6</v>
       </c>
@@ -3322,7 +3520,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
         <v>6</v>
       </c>
@@ -3342,7 +3540,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
         <v>6</v>
       </c>
@@ -3362,7 +3560,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
         <v>6</v>
       </c>
@@ -3382,7 +3580,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
         <v>6</v>
       </c>
@@ -3402,7 +3600,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
         <v>6</v>
       </c>
@@ -3422,7 +3620,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
         <v>6</v>
       </c>
@@ -3442,7 +3640,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
         <v>6</v>
       </c>
@@ -3462,7 +3660,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
         <v>6</v>
       </c>
@@ -3482,7 +3680,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
         <v>6</v>
       </c>
@@ -3502,7 +3700,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
         <v>6</v>
       </c>
@@ -3522,7 +3720,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
         <v>6</v>
       </c>
@@ -3542,7 +3740,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
         <v>6</v>
       </c>
@@ -3562,7 +3760,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
         <v>6</v>
       </c>
@@ -3582,7 +3780,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
         <v>6</v>
       </c>
@@ -3602,7 +3800,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
         <v>6</v>
       </c>
@@ -3622,7 +3820,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="s">
         <v>6</v>
       </c>
@@ -3642,7 +3840,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
         <v>6</v>
       </c>
@@ -3662,7 +3860,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="s">
         <v>6</v>
       </c>
@@ -3682,7 +3880,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
         <v>6</v>
       </c>
@@ -3702,7 +3900,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="s">
         <v>6</v>
       </c>
@@ -3722,7 +3920,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
         <v>6</v>
       </c>
@@ -3742,7 +3940,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A169" s="1" t="s">
         <v>6</v>
       </c>
@@ -3762,7 +3960,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
         <v>6</v>
       </c>
@@ -3782,7 +3980,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A171" s="1" t="s">
         <v>6</v>
       </c>
@@ -3802,7 +4000,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="s">
         <v>6</v>
       </c>
@@ -3822,7 +4020,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A173" s="1" t="s">
         <v>6</v>
       </c>
@@ -3842,7 +4040,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="s">
         <v>6</v>
       </c>
@@ -3862,7 +4060,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A175" s="1" t="s">
         <v>6</v>
       </c>
@@ -3882,7 +4080,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="s">
         <v>6</v>
       </c>
@@ -3902,7 +4100,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A177" s="1" t="s">
         <v>6</v>
       </c>
@@ -3922,7 +4120,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="s">
         <v>6</v>
       </c>
@@ -3942,7 +4140,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A179" s="1" t="s">
         <v>6</v>
       </c>
@@ -3962,7 +4160,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="s">
         <v>6</v>
       </c>
@@ -3982,7 +4180,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A181" s="1" t="s">
         <v>6</v>
       </c>
@@ -4002,7 +4200,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A182" s="1" t="s">
         <v>6</v>
       </c>
@@ -4022,7 +4220,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A183" s="1" t="s">
         <v>6</v>
       </c>
@@ -4042,7 +4240,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A184" s="1" t="s">
         <v>6</v>
       </c>
@@ -4062,7 +4260,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A185" s="1" t="s">
         <v>6</v>
       </c>
@@ -4082,7 +4280,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A186" s="1" t="s">
         <v>6</v>
       </c>
@@ -4102,7 +4300,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A187" s="1" t="s">
         <v>6</v>
       </c>
@@ -4122,7 +4320,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A188" s="1" t="s">
         <v>6</v>
       </c>
@@ -4142,7 +4340,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A189" s="1" t="s">
         <v>6</v>
       </c>
@@ -4162,7 +4360,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A190" s="1" t="s">
         <v>6</v>
       </c>
@@ -4182,7 +4380,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A191" s="1" t="s">
         <v>6</v>
       </c>
@@ -4202,7 +4400,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A192" s="1" t="s">
         <v>6</v>
       </c>
@@ -4222,7 +4420,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A193" s="1" t="s">
         <v>6</v>
       </c>
@@ -4248,14 +4446,14 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F193"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="16384" width="8.90625" style="1"/>
+    <col min="1" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4275,7 +4473,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -4295,7 +4493,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -4315,7 +4513,7 @@
         <v>-8</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -4335,7 +4533,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -4355,7 +4553,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -4375,7 +4573,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
@@ -4395,7 +4593,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -4415,7 +4613,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -4435,7 +4633,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
@@ -4455,7 +4653,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>7</v>
       </c>
@@ -4475,7 +4673,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>7</v>
       </c>
@@ -4495,7 +4693,7 @@
         <v>-8</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>7</v>
       </c>
@@ -4515,7 +4713,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>7</v>
       </c>
@@ -4535,7 +4733,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>7</v>
       </c>
@@ -4555,7 +4753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>7</v>
       </c>
@@ -4575,7 +4773,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>7</v>
       </c>
@@ -4595,7 +4793,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>7</v>
       </c>
@@ -4615,7 +4813,7 @@
         <v>-8</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>7</v>
       </c>
@@ -4635,7 +4833,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>7</v>
       </c>
@@ -4655,7 +4853,7 @@
         <v>-9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>7</v>
       </c>
@@ -4675,7 +4873,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>7</v>
       </c>
@@ -4695,7 +4893,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>7</v>
       </c>
@@ -4715,7 +4913,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>7</v>
       </c>
@@ -4735,7 +4933,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>7</v>
       </c>
@@ -4755,7 +4953,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>7</v>
       </c>
@@ -4775,7 +4973,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>7</v>
       </c>
@@ -4795,7 +4993,7 @@
         <v>-8</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>7</v>
       </c>
@@ -4815,7 +5013,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>7</v>
       </c>
@@ -4835,7 +5033,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>7</v>
       </c>
@@ -4855,7 +5053,7 @@
         <v>-8</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>7</v>
       </c>
@@ -4875,7 +5073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>7</v>
       </c>
@@ -4895,7 +5093,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>7</v>
       </c>
@@ -4915,7 +5113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>7</v>
       </c>
@@ -4935,7 +5133,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>7</v>
       </c>
@@ -4955,7 +5153,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>7</v>
       </c>
@@ -4975,7 +5173,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>7</v>
       </c>
@@ -4995,7 +5193,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>7</v>
       </c>
@@ -5015,7 +5213,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>7</v>
       </c>
@@ -5035,7 +5233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>7</v>
       </c>
@@ -5055,7 +5253,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>7</v>
       </c>
@@ -5075,7 +5273,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>7</v>
       </c>
@@ -5095,7 +5293,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>7</v>
       </c>
@@ -5115,7 +5313,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>7</v>
       </c>
@@ -5135,7 +5333,7 @@
         <v>-6</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>7</v>
       </c>
@@ -5155,7 +5353,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>7</v>
       </c>
@@ -5175,7 +5373,7 @@
         <v>-9</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>7</v>
       </c>
@@ -5195,7 +5393,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>7</v>
       </c>
@@ -5215,7 +5413,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>7</v>
       </c>
@@ -5235,7 +5433,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>7</v>
       </c>
@@ -5255,7 +5453,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>7</v>
       </c>
@@ -5275,7 +5473,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>7</v>
       </c>
@@ -5295,7 +5493,7 @@
         <v>-8</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>7</v>
       </c>
@@ -5315,7 +5513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>7</v>
       </c>
@@ -5335,7 +5533,7 @@
         <v>-8</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>7</v>
       </c>
@@ -5355,7 +5553,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>7</v>
       </c>
@@ -5375,7 +5573,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>7</v>
       </c>
@@ -5395,7 +5593,7 @@
         <v>-9</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>7</v>
       </c>
@@ -5415,7 +5613,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>7</v>
       </c>
@@ -5435,7 +5633,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>7</v>
       </c>
@@ -5455,7 +5653,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>7</v>
       </c>
@@ -5475,7 +5673,7 @@
         <v>-6</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>7</v>
       </c>
@@ -5495,7 +5693,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>7</v>
       </c>
@@ -5515,7 +5713,7 @@
         <v>-8</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>7</v>
       </c>
@@ -5535,7 +5733,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>7</v>
       </c>
@@ -5555,7 +5753,7 @@
         <v>-9</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>7</v>
       </c>
@@ -5575,7 +5773,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>7</v>
       </c>
@@ -5595,7 +5793,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>7</v>
       </c>
@@ -5615,7 +5813,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>7</v>
       </c>
@@ -5635,7 +5833,7 @@
         <v>-8</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>7</v>
       </c>
@@ -5655,7 +5853,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>7</v>
       </c>
@@ -5675,7 +5873,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>7</v>
       </c>
@@ -5695,7 +5893,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>7</v>
       </c>
@@ -5715,7 +5913,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>7</v>
       </c>
@@ -5735,7 +5933,7 @@
         <v>-6</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>7</v>
       </c>
@@ -5755,7 +5953,7 @@
         <v>-9</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>7</v>
       </c>
@@ -5775,7 +5973,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>7</v>
       </c>
@@ -5795,7 +5993,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>7</v>
       </c>
@@ -5815,7 +6013,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>7</v>
       </c>
@@ -5835,7 +6033,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>7</v>
       </c>
@@ -5855,7 +6053,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>7</v>
       </c>
@@ -5875,7 +6073,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>7</v>
       </c>
@@ -5895,7 +6093,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
         <v>7</v>
       </c>
@@ -5915,7 +6113,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>7</v>
       </c>
@@ -5935,7 +6133,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>7</v>
       </c>
@@ -5955,7 +6153,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>7</v>
       </c>
@@ -5975,7 +6173,7 @@
         <v>-6</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
         <v>7</v>
       </c>
@@ -5995,7 +6193,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
         <v>7</v>
       </c>
@@ -6015,7 +6213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>7</v>
       </c>
@@ -6035,7 +6233,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>7</v>
       </c>
@@ -6055,7 +6253,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
         <v>7</v>
       </c>
@@ -6075,7 +6273,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>7</v>
       </c>
@@ -6095,7 +6293,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
         <v>7</v>
       </c>
@@ -6115,7 +6313,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
         <v>7</v>
       </c>
@@ -6135,7 +6333,7 @@
         <v>-6</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
         <v>7</v>
       </c>
@@ -6155,7 +6353,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
         <v>7</v>
       </c>
@@ -6175,7 +6373,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
         <v>7</v>
       </c>
@@ -6195,7 +6393,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
         <v>7</v>
       </c>
@@ -6215,7 +6413,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
         <v>7</v>
       </c>
@@ -6235,7 +6433,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
         <v>7</v>
       </c>
@@ -6255,7 +6453,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
         <v>7</v>
       </c>
@@ -6275,7 +6473,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
         <v>7</v>
       </c>
@@ -6295,7 +6493,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
         <v>7</v>
       </c>
@@ -6315,7 +6513,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
         <v>7</v>
       </c>
@@ -6335,7 +6533,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
         <v>7</v>
       </c>
@@ -6355,7 +6553,7 @@
         <v>-9</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
         <v>7</v>
       </c>
@@ -6375,7 +6573,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
         <v>7</v>
       </c>
@@ -6395,7 +6593,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
         <v>7</v>
       </c>
@@ -6415,7 +6613,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
         <v>7</v>
       </c>
@@ -6435,7 +6633,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
         <v>7</v>
       </c>
@@ -6455,7 +6653,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
         <v>7</v>
       </c>
@@ -6475,7 +6673,7 @@
         <v>-6</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
         <v>7</v>
       </c>
@@ -6495,7 +6693,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
         <v>7</v>
       </c>
@@ -6515,7 +6713,7 @@
         <v>-9</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
         <v>7</v>
       </c>
@@ -6535,7 +6733,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
         <v>7</v>
       </c>
@@ -6555,7 +6753,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
         <v>7</v>
       </c>
@@ -6575,7 +6773,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
         <v>7</v>
       </c>
@@ -6595,7 +6793,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
         <v>7</v>
       </c>
@@ -6615,7 +6813,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
         <v>7</v>
       </c>
@@ -6635,7 +6833,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
         <v>7</v>
       </c>
@@ -6655,7 +6853,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
         <v>7</v>
       </c>
@@ -6675,7 +6873,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
         <v>7</v>
       </c>
@@ -6695,7 +6893,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
         <v>7</v>
       </c>
@@ -6715,7 +6913,7 @@
         <v>-9</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
         <v>7</v>
       </c>
@@ -6735,7 +6933,7 @@
         <v>-8</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
         <v>7</v>
       </c>
@@ -6755,7 +6953,7 @@
         <v>-8</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
         <v>7</v>
       </c>
@@ -6775,7 +6973,7 @@
         <v>-8</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
         <v>7</v>
       </c>
@@ -6795,7 +6993,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
         <v>7</v>
       </c>
@@ -6815,7 +7013,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
         <v>7</v>
       </c>
@@ -6835,7 +7033,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
         <v>7</v>
       </c>
@@ -6855,7 +7053,7 @@
         <v>-6</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
         <v>7</v>
       </c>
@@ -6875,7 +7073,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
         <v>7</v>
       </c>
@@ -6895,7 +7093,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
         <v>7</v>
       </c>
@@ -6915,7 +7113,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
         <v>7</v>
       </c>
@@ -6935,7 +7133,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
         <v>7</v>
       </c>
@@ -6955,7 +7153,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
         <v>7</v>
       </c>
@@ -6975,7 +7173,7 @@
         <v>-6</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
         <v>7</v>
       </c>
@@ -6995,7 +7193,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
         <v>7</v>
       </c>
@@ -7015,7 +7213,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
         <v>7</v>
       </c>
@@ -7035,7 +7233,7 @@
         <v>-6</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
         <v>7</v>
       </c>
@@ -7055,7 +7253,7 @@
         <v>-8</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
         <v>7</v>
       </c>
@@ -7075,7 +7273,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
         <v>7</v>
       </c>
@@ -7095,7 +7293,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
         <v>7</v>
       </c>
@@ -7115,7 +7313,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
         <v>7</v>
       </c>
@@ -7135,7 +7333,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
         <v>7</v>
       </c>
@@ -7155,7 +7353,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
         <v>7</v>
       </c>
@@ -7175,7 +7373,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
         <v>7</v>
       </c>
@@ -7195,7 +7393,7 @@
         <v>-9</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
         <v>7</v>
       </c>
@@ -7215,7 +7413,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
         <v>7</v>
       </c>
@@ -7235,7 +7433,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
         <v>7</v>
       </c>
@@ -7255,7 +7453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
         <v>7</v>
       </c>
@@ -7275,7 +7473,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
         <v>7</v>
       </c>
@@ -7295,7 +7493,7 @@
         <v>-8</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
         <v>7</v>
       </c>
@@ -7315,7 +7513,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
         <v>7</v>
       </c>
@@ -7335,7 +7533,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
         <v>7</v>
       </c>
@@ -7355,7 +7553,7 @@
         <v>-8</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
         <v>7</v>
       </c>
@@ -7375,7 +7573,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
         <v>7</v>
       </c>
@@ -7395,7 +7593,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
         <v>7</v>
       </c>
@@ -7415,7 +7613,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
         <v>7</v>
       </c>
@@ -7435,7 +7633,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
         <v>7</v>
       </c>
@@ -7455,7 +7653,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
         <v>7</v>
       </c>
@@ -7475,7 +7673,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
         <v>7</v>
       </c>
@@ -7495,7 +7693,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="s">
         <v>7</v>
       </c>
@@ -7515,7 +7713,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
         <v>7</v>
       </c>
@@ -7535,7 +7733,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="s">
         <v>7</v>
       </c>
@@ -7555,7 +7753,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
         <v>7</v>
       </c>
@@ -7575,7 +7773,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="s">
         <v>7</v>
       </c>
@@ -7595,7 +7793,7 @@
         <v>-9</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
         <v>7</v>
       </c>
@@ -7615,7 +7813,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A169" s="1" t="s">
         <v>7</v>
       </c>
@@ -7635,7 +7833,7 @@
         <v>-8</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
         <v>7</v>
       </c>
@@ -7655,7 +7853,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A171" s="1" t="s">
         <v>7</v>
       </c>
@@ -7675,7 +7873,7 @@
         <v>-9</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="s">
         <v>7</v>
       </c>
@@ -7695,7 +7893,7 @@
         <v>-8</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A173" s="1" t="s">
         <v>7</v>
       </c>
@@ -7715,7 +7913,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="s">
         <v>7</v>
       </c>
@@ -7735,7 +7933,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A175" s="1" t="s">
         <v>7</v>
       </c>
@@ -7755,7 +7953,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="s">
         <v>7</v>
       </c>
@@ -7775,7 +7973,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A177" s="1" t="s">
         <v>7</v>
       </c>
@@ -7795,7 +7993,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="s">
         <v>7</v>
       </c>
@@ -7815,7 +8013,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A179" s="1" t="s">
         <v>7</v>
       </c>
@@ -7835,7 +8033,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="s">
         <v>7</v>
       </c>
@@ -7855,7 +8053,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A181" s="1" t="s">
         <v>7</v>
       </c>
@@ -7875,7 +8073,7 @@
         <v>-6</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A182" s="1" t="s">
         <v>7</v>
       </c>
@@ -7895,7 +8093,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A183" s="1" t="s">
         <v>7</v>
       </c>
@@ -7915,7 +8113,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A184" s="1" t="s">
         <v>7</v>
       </c>
@@ -7935,7 +8133,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A185" s="1" t="s">
         <v>7</v>
       </c>
@@ -7955,7 +8153,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A186" s="1" t="s">
         <v>7</v>
       </c>
@@ -7975,7 +8173,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A187" s="1" t="s">
         <v>7</v>
       </c>
@@ -7995,7 +8193,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A188" s="1" t="s">
         <v>7</v>
       </c>
@@ -8015,7 +8213,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A189" s="1" t="s">
         <v>7</v>
       </c>
@@ -8035,7 +8233,7 @@
         <v>-9</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A190" s="1" t="s">
         <v>7</v>
       </c>
@@ -8055,7 +8253,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A191" s="1" t="s">
         <v>7</v>
       </c>
@@ -8075,7 +8273,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A192" s="1" t="s">
         <v>7</v>
       </c>
@@ -8095,7 +8293,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A193" s="1" t="s">
         <v>7</v>
       </c>
@@ -8118,4 +8316,3879 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F193"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" width="8.88671875" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A55" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A61" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A63" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A64" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A65" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A67" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A68" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A69" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A70" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A71" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A73" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A74" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A75" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A77" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A78" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A79" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A80" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A82" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A84" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A85" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A86" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A87" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A88" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A90" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A92" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A93" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A95" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A97" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A98" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A99" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A103" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F103" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A104" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A105" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E105" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F105" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A106" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A107" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E107" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F107" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A108" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F108" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A109" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E109" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F109" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A110" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F110" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A111" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F111" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A112" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F112" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A113" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F113" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A114" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F114" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A115" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F115" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A116" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F116" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A117" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F117" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A118" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F118" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A119" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F119" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A120" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F120" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A121" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F121" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A122" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F122" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A123" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E123" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F123" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A124" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F124" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A125" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D125" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E125" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F125" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A126" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D126" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E126" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F126" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A127" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D127" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E127" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F127" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A128" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E128" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F128" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A129" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D129" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E129" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F129" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A130" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E130" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F130" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A131" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C131" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D131" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E131" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F131" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A132" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C132" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E132" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F132" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A133" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C133" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D133" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E133" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F133" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A134" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C134" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D134" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E134" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F134" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A135" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C135" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D135" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E135" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F135" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A136" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B136" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C136" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D136" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E136" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F136" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A137" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C137" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D137" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E137" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F137" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A138" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C138" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D138" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E138" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F138" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A139" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B139" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D139" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E139" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F139" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A140" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B140" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D140" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E140" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F140" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A141" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B141" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C141" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D141" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E141" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F141" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A142" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C142" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D142" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E142" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F142" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A143" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C143" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D143" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E143" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F143" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A144" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C144" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D144" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E144" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F144" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A145" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D145" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E145" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F145" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A146" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B146" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C146" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D146" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E146" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F146" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A147" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C147" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D147" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E147" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F147" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A148" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B148" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D148" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E148" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F148" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A149" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B149" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C149" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D149" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E149" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F149" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A150" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B150" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C150" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D150" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E150" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F150" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A151" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B151" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C151" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D151" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E151" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F151" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A152" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B152" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C152" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D152" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E152" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F152" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A153" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B153" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C153" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D153" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E153" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F153" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A154" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B154" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C154" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D154" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E154" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F154" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A155" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B155" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C155" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D155" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E155" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F155" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A156" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B156" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C156" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D156" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E156" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F156" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A157" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B157" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C157" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D157" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E157" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F157" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A158" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B158" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C158" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D158" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E158" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F158" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A159" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B159" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C159" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D159" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E159" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F159" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A160" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B160" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C160" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D160" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E160" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F160" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A161" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B161" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C161" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D161" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E161" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F161" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A162" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B162" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C162" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D162" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E162" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F162" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A163" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B163" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C163" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D163" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E163" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F163" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A164" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B164" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C164" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D164" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E164" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F164" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A165" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B165" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C165" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D165" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E165" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F165" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A166" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B166" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C166" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D166" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E166" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F166" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A167" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B167" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C167" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D167" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E167" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F167" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A168" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B168" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C168" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D168" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E168" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F168" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A169" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B169" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C169" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D169" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E169" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F169" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A170" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B170" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C170" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D170" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E170" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F170" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A171" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B171" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C171" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D171" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E171" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F171" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A172" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B172" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C172" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D172" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E172" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F172" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A173" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B173" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C173" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D173" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E173" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F173" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A174" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B174" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C174" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D174" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E174" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F174" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A175" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B175" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C175" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D175" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E175" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F175" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A176" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B176" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C176" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D176" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E176" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F176" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A177" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B177" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C177" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D177" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E177" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F177" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A178" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B178" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C178" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D178" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E178" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F178" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A179" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B179" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C179" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D179" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E179" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F179" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A180" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B180" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C180" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D180" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E180" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F180" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A181" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B181" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C181" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D181" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E181" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F181" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A182" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B182" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C182" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D182" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E182" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F182" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A183" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B183" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C183" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D183" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E183" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F183" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A184" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B184" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C184" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D184" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E184" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F184" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A185" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B185" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C185" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D185" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E185" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F185" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A186" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B186" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C186" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D186" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E186" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F186" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A187" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B187" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C187" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D187" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E187" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F187" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A188" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B188" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C188" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D188" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E188" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F188" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A189" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B189" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C189" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D189" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E189" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F189" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A190" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B190" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C190" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D190" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E190" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F190" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A191" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B191" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C191" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D191" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E191" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F191" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A192" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B192" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C192" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D192" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E192" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F192" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A193" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B193" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C193" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D193" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E193" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F193" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>